--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -50,7 +50,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JDV Modalite Demande Acte Iimagerie CISIS</t>
+    <t>JDV Modalite Demande Acte Imagerie CISIS</t>
   </si>
   <si>
     <t>Status</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,85 +101,85 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C63334</t>
+    <t>MED-1126</t>
+  </si>
+  <si>
+    <t>Radiographie sans contraste</t>
+  </si>
+  <si>
+    <t>MED-1127</t>
+  </si>
+  <si>
+    <t>Radiographie avec contraste</t>
+  </si>
+  <si>
+    <t>MED-1128</t>
+  </si>
+  <si>
+    <t>Échographie sans contraste</t>
+  </si>
+  <si>
+    <t>MED-1129</t>
+  </si>
+  <si>
+    <t>Échographie avec contraste</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Mammographie</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>Scanner/TDM</t>
+  </si>
+  <si>
+    <t>MR</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>Autre technique d'imagerie</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>Scintigraphie</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>TEP : Tomographie par émission de positons</t>
+  </si>
+  <si>
+    <t>http://dicom.nema.org/resources/ontology/DCM</t>
+  </si>
+  <si>
+    <t>258174001</t>
   </si>
   <si>
     <t>imagerie interventionnelle</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>MED-1126</t>
-  </si>
-  <si>
-    <t>Radiographie sans contraste</t>
-  </si>
-  <si>
-    <t>MED-1127</t>
-  </si>
-  <si>
-    <t>Radiographie avec contraste</t>
-  </si>
-  <si>
-    <t>MED-1128</t>
-  </si>
-  <si>
-    <t>Échographie sans contraste</t>
-  </si>
-  <si>
-    <t>MED-1129</t>
-  </si>
-  <si>
-    <t>Échographie avec contraste</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
-  </si>
-  <si>
-    <t>MG</t>
-  </si>
-  <si>
-    <t>Mammographie</t>
-  </si>
-  <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>Scanner/TDM</t>
-  </si>
-  <si>
-    <t>MR</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>OT</t>
-  </si>
-  <si>
-    <t>Autre technique d'imagerie</t>
-  </si>
-  <si>
-    <t>NM</t>
-  </si>
-  <si>
-    <t>Scintigraphie</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>TEP : Tomographie par émission de positons</t>
-  </si>
-  <si>
-    <t>http://dicom.nema.org/resources/ontology/DCM</t>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -443,52 +443,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -506,50 +460,50 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -557,7 +511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -576,65 +530,111 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>54</v>
       </c>
     </row>

--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
+++ b/www/terminologies/ValueSet-jdv-modalite-demande-acte-imagerie-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
